--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
@@ -2509,11 +2509,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="58209079"/>
-        <c:axId val="84132854"/>
+        <c:axId val="98577793"/>
+        <c:axId val="21619261"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="58209079"/>
+        <c:axId val="98577793"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2547,7 +2547,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84132854"/>
+        <c:crossAx val="21619261"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="84132854"/>
+        <c:axId val="21619261"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58209079"/>
+        <c:crossAx val="98577793"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -6202,7 +6202,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -6754,23 +6754,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="AH86" s="22" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="22"/>
       <c r="AJ86" s="22"/>
@@ -10297,7 +10297,7 @@
       <c r="AP86" s="22"/>
       <c r="AQ86" s="22" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15131,15 +15131,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>80.9606713198364</v>
+        <v>82.121397399082</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -15245,23 +15245,23 @@
       </c>
       <c r="T2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="H39" s="27" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="27"/>
       <c r="J39" s="27"/>
@@ -16276,7 +16276,7 @@
       <c r="P39" s="27"/>
       <c r="Q39" s="27" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
@@ -2509,11 +2509,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="98577793"/>
-        <c:axId val="21619261"/>
+        <c:axId val="1273239"/>
+        <c:axId val="82494618"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="98577793"/>
+        <c:axId val="1273239"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2547,7 +2547,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21619261"/>
+        <c:crossAx val="82494618"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="21619261"/>
+        <c:axId val="82494618"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98577793"/>
+        <c:crossAx val="1273239"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
@@ -2509,11 +2509,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="1273239"/>
-        <c:axId val="82494618"/>
+        <c:axId val="60953702"/>
+        <c:axId val="94543418"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1273239"/>
+        <c:axId val="60953702"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2547,7 +2547,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82494618"/>
+        <c:crossAx val="94543418"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="82494618"/>
+        <c:axId val="94543418"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1273239"/>
+        <c:crossAx val="60953702"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
@@ -2509,11 +2509,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="60953702"/>
-        <c:axId val="94543418"/>
+        <c:axId val="25074911"/>
+        <c:axId val="11183174"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="60953702"/>
+        <c:axId val="25074911"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2547,7 +2547,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94543418"/>
+        <c:crossAx val="11183174"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="94543418"/>
+        <c:axId val="11183174"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60953702"/>
+        <c:crossAx val="25074911"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
